--- a/backtest_runs/20260410_193731/by_symbol/JDWS/JDWS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/JDWS/JDWS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-2744.679999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>97255.32000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100571.12</v>
@@ -771,7 +771,7 @@
         <v>-2666.799999999989</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>97904.32000000001</v>
@@ -817,7 +817,7 @@
         <v>-67.2600000000059</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>97837.06000000001</v>
@@ -909,7 +909,7 @@
         <v>-3905.800000000003</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>97930.28</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>97946.8</v>
@@ -1093,7 +1093,7 @@
         <v>-1460.839999999999</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>96485.96000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-273.7599999999925</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>100113.28</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>100113.28</v>
@@ -1323,7 +1323,7 @@
         <v>-1043.120000000004</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>99070.16</v>
@@ -1461,7 +1461,7 @@
         <v>-2566.5</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>99839.52000000002</v>
